--- a/ARM Functions/Item Edits/Mega Stone Long Reach.xlsx
+++ b/ARM Functions/Item Edits/Mega Stone Long Reach.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Item Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E64C643-0D0B-44A2-8C17-022954E8C5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B3E04F-7B90-4023-82D0-94B6C0122EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{6B563214-6527-4E5F-B5EA-E821D6DED3A7}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>notes</t>
   </si>
@@ -99,12 +99,6 @@
     <t>bl 0x00092298</t>
   </si>
   <si>
-    <t>ldrh r0, [r0, 0xC]</t>
-  </si>
-  <si>
-    <t>BC00D0E1</t>
-  </si>
-  <si>
     <t>mov r1, 0x3</t>
   </si>
   <si>
@@ -132,42 +126,9 @@
     <t>get species</t>
   </si>
   <si>
-    <t>34109FE5</t>
-  </si>
-  <si>
     <t>get table</t>
   </si>
   <si>
-    <t>0020A0E3</t>
-  </si>
-  <si>
-    <t>mov r2, 0x0</t>
-  </si>
-  <si>
-    <t>B23091E1</t>
-  </si>
-  <si>
-    <t>ldrh r3, [r1, r2]</t>
-  </si>
-  <si>
-    <t>030050E1</t>
-  </si>
-  <si>
-    <t>cmp r0, r3</t>
-  </si>
-  <si>
-    <t>000050E3</t>
-  </si>
-  <si>
-    <t>cmp r0, 0x0</t>
-  </si>
-  <si>
-    <t>022082E2</t>
-  </si>
-  <si>
-    <t>add r2, r2, 0x2</t>
-  </si>
-  <si>
     <t>0F40BDE8</t>
   </si>
   <si>
@@ -177,12 +138,6 @@
     <t>0F80BDE8</t>
   </si>
   <si>
-    <t>Table of valid Pokemon</t>
-  </si>
-  <si>
-    <t>Table</t>
-  </si>
-  <si>
     <t>Mega Stone Long Reach 0x2D/0x4A/0x41</t>
   </si>
   <si>
@@ -201,27 +156,6 @@
     <t>blo 0x000DADA4</t>
   </si>
   <si>
-    <t>Blaziken</t>
-  </si>
-  <si>
-    <t>Gallade</t>
-  </si>
-  <si>
-    <t>Kangaskhan</t>
-  </si>
-  <si>
-    <t>Lopunny</t>
-  </si>
-  <si>
-    <t>Medicham</t>
-  </si>
-  <si>
-    <t>Metagross</t>
-  </si>
-  <si>
-    <t>0014AF80</t>
-  </si>
-  <si>
     <t>000D5E1C</t>
   </si>
   <si>
@@ -234,22 +168,28 @@
     <t>BDCEFEEB</t>
   </si>
   <si>
-    <t>ABDDFF0A</t>
-  </si>
-  <si>
-    <t>AEDDFF0A</t>
-  </si>
-  <si>
-    <t>A0DDFFEA</t>
-  </si>
-  <si>
-    <t>08FFFF0A</t>
-  </si>
-  <si>
-    <t>72F1FF3A</t>
-  </si>
-  <si>
-    <t>9F79008A</t>
+    <t>bl 0x000D6F98</t>
+  </si>
+  <si>
+    <t>cmp r1, 0x1</t>
+  </si>
+  <si>
+    <t>FCE1FFEB</t>
+  </si>
+  <si>
+    <t>010051E3</t>
+  </si>
+  <si>
+    <t>0400001A</t>
+  </si>
+  <si>
+    <t>0FFFFF0A</t>
+  </si>
+  <si>
+    <t>79F1FF3A</t>
+  </si>
+  <si>
+    <t>A679008A</t>
   </si>
 </sst>
 </file>
@@ -654,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B45B0BF-76E7-4635-9005-9D6B1877FAE8}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -691,14 +631,14 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(C3,1),"10A0E3")</f>
         <v>0310A0E3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -756,18 +696,18 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -776,25 +716,25 @@
         <v>000DE794</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="str">
-        <f t="shared" ref="A12:A30" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
+        <f t="shared" ref="A12:A22" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
         <v>000DE798</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" s="5"/>
     </row>
@@ -804,7 +744,7 @@
         <v>000DE79C</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>12</v>
@@ -817,13 +757,13 @@
         <v>000DE7A0</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -831,15 +771,14 @@
         <f t="shared" si="1"/>
         <v>000DE7A4</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="2" t="str">
-        <f>_xlfn.CONCAT("ldr r1, [pc, #",HEX2DEC(A30)-HEX2DEC(A15)-8,"]")</f>
-        <v>ldr r1, [pc, #52]</v>
+      <c r="B15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -848,10 +787,11 @@
         <v>000DE7A8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>27</v>
+        <v>40</v>
+      </c>
+      <c r="C16" s="2" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A22)</f>
+        <v>bne 0x000DE7C0</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -860,10 +800,11 @@
         <v>000DE7AC</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="C17" s="2" t="str">
+        <f>SUBSTITUTE(C10,"push","pop")</f>
+        <v>pop {r0, r1, r2, r3, lr}</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -872,10 +813,10 @@
         <v>000DE7B0</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -884,11 +825,10 @@
         <v>000DE7B4</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="2" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A24)</f>
-        <v>beq 0x000DE7C8</v>
+        <v>41</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -896,11 +836,14 @@
         <f t="shared" si="1"/>
         <v>000DE7B8</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>32</v>
+      <c r="B20" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -909,11 +852,13 @@
         <v>000DE7BC</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="2" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A29)</f>
-        <v>beq 0x000DE7DC</v>
+        <v>43</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -921,381 +866,34 @@
         <f t="shared" si="1"/>
         <v>000DE7C0</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DE7C4</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="2" t="str">
-        <f>_xlfn.CONCAT("b 0x",A17)</f>
-        <v>b 0x000DE7AC</v>
+      <c r="B22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="2" t="str">
+        <f>SUBSTITUTE(C17,"lr","pc")</f>
+        <v>pop {r0, r1, r2, r3, pc}</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DE7C8</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="2" t="str">
-        <f>SUBSTITUTE(C10,"push","pop")</f>
-        <v>pop {r0, r1, r2, r3, lr}</v>
-      </c>
+      <c r="A24" s="1"/>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DE7CC</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="C25" s="6"/>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DE7D0</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="C26" s="6"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DE7D4</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="C27" s="6"/>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DE7D8</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="C28" s="6"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DE7DC</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="2" t="str">
-        <f>SUBSTITUTE(C24,"lr","pc")</f>
-        <v>pop {r0, r1, r2, r3, pc}</v>
-      </c>
+      <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>000DE7E0</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B33" s="2" t="str">
-        <f>RIGHT(E33,2)&amp;LEFT(E33,2)</f>
-        <v>0101</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" s="2">
-        <v>257</v>
-      </c>
-      <c r="E33" s="2" t="str">
-        <f>DEC2HEX(D33,4)</f>
-        <v>0101</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="2" t="str">
-        <f>DEC2HEX(HEX2DEC(A33)+2,8)</f>
-        <v>0014AF82</v>
-      </c>
-      <c r="B34" s="2" t="str">
-        <f t="shared" ref="B34:B48" si="2">RIGHT(E34,2)&amp;LEFT(E34,2)</f>
-        <v>DB01</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" s="2">
-        <v>475</v>
-      </c>
-      <c r="E34" s="2" t="str">
-        <f t="shared" ref="E34:E48" si="3">DEC2HEX(D34,4)</f>
-        <v>01DB</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="2" t="str">
-        <f t="shared" ref="A35:A48" si="4">DEC2HEX(HEX2DEC(A34)+2,8)</f>
-        <v>0014AF84</v>
-      </c>
-      <c r="B35" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>7300</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D35" s="2">
-        <v>115</v>
-      </c>
-      <c r="E35" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0073</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF86</v>
-      </c>
-      <c r="B36" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>AC01</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D36" s="2">
-        <v>428</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>01AC</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF88</v>
-      </c>
-      <c r="B37" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>3401</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D37" s="2">
-        <v>308</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0134</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF8A</v>
-      </c>
-      <c r="B38" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>7801</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" s="2">
-        <v>376</v>
-      </c>
-      <c r="E38" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0178</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF8C</v>
-      </c>
-      <c r="B39" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E39" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF8E</v>
-      </c>
-      <c r="B40" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E40" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF90</v>
-      </c>
-      <c r="B41" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E41" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF92</v>
-      </c>
-      <c r="B42" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF94</v>
-      </c>
-      <c r="B43" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E43" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF96</v>
-      </c>
-      <c r="B44" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E44" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF98</v>
-      </c>
-      <c r="B45" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E45" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF9A</v>
-      </c>
-      <c r="B46" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E46" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF9C</v>
-      </c>
-      <c r="B47" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E47" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF9E</v>
-      </c>
-      <c r="B48" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E48" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
+      <c r="C30" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
